--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="7"/>
+    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -15315,6 +15315,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>技嘉</t>
     </r>
     <r>
@@ -15947,8 +15953,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Chilanka"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -15959,18 +15978,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3" tint="-0.25"/>
-      <name val="Chilanka"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -15980,21 +15992,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF212121"/>
-      <name val="AR PL UKai CN"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -18891,6 +18897,9 @@
       <c r="C11" s="1">
         <v>46064</v>
       </c>
+      <c r="D11">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
@@ -18898,6 +18907,9 @@
       </c>
       <c r="C12" s="1">
         <v>46065</v>
+      </c>
+      <c r="D12">
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:4">

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -15953,16 +15953,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3" tint="-0.25"/>
-      <name val="Chilanka"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15978,17 +15971,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Chilanka"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15999,8 +15992,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -16853,19 +16853,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>635</xdr:colOff>
+      <xdr:colOff>505460</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>153670</xdr:rowOff>
+      <xdr:rowOff>86360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>381635</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>106045</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>391160</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>162560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPr id="3" name="图片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -16878,50 +16878,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="635" y="153670"/>
-          <a:ext cx="23698200" cy="8410575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>534035</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>162560</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>581660</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>162560</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14250035" y="1076960"/>
-          <a:ext cx="4848225" cy="6858000"/>
+          <a:off x="505460" y="86360"/>
+          <a:ext cx="18402300" cy="7391400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -18768,18 +18726,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="3"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1">
         <v>46023</v>
       </c>
       <c r="C1" s="1">
         <v>46054</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>46024</v>
       </c>
@@ -18789,8 +18750,14 @@
       <c r="D2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="1">
+        <v>46083</v>
+      </c>
+      <c r="F2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>46025</v>
       </c>
@@ -18800,8 +18767,14 @@
       <c r="D3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="1">
+        <v>46084</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>46026</v>
       </c>
@@ -18811,8 +18784,14 @@
       <c r="D4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="1">
+        <v>46085</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>46027</v>
       </c>
@@ -18825,8 +18804,11 @@
       <c r="D5">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>46028</v>
       </c>
@@ -18839,8 +18821,14 @@
       <c r="D6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="1">
+        <v>46087</v>
+      </c>
+      <c r="F6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>46029</v>
       </c>
@@ -18853,8 +18841,14 @@
       <c r="D7">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="1">
+        <v>46088</v>
+      </c>
+      <c r="F7">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>46030</v>
       </c>
@@ -18864,8 +18858,14 @@
       <c r="C8" s="1">
         <v>46061</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="1">
+        <v>46089</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>46031</v>
       </c>
@@ -18878,8 +18878,14 @@
       <c r="D9">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="1">
+        <v>46090</v>
+      </c>
+      <c r="F9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>46032</v>
       </c>
@@ -18889,8 +18895,11 @@
       <c r="D10">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>46033</v>
       </c>
@@ -18900,8 +18909,14 @@
       <c r="D11">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="1">
+        <v>46092</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>46034</v>
       </c>
@@ -18911,8 +18926,11 @@
       <c r="D12">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>46035</v>
       </c>
@@ -18922,64 +18940,103 @@
       <c r="C13" s="1">
         <v>46066</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>46036</v>
       </c>
       <c r="C14" s="1">
         <v>46067</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="1">
+        <v>46095</v>
+      </c>
+      <c r="F14">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>46037</v>
       </c>
       <c r="C15" s="1">
         <v>46068</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="1">
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>46038</v>
       </c>
       <c r="C16" s="1">
         <v>46069</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="E16" s="1">
+        <v>46097</v>
+      </c>
+      <c r="F16">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
       <c r="C17" s="1">
         <v>46070</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="E17" s="1">
+        <v>46098</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
       <c r="C18" s="1">
         <v>46071</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="E18" s="1">
+        <v>46099</v>
+      </c>
+      <c r="F18">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
       <c r="C19" s="1">
         <v>46072</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="E19" s="1">
+        <v>46100</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
       <c r="C20" s="1">
         <v>46073</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="E20" s="1">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -18989,56 +19046,83 @@
       <c r="C21" s="1">
         <v>46074</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="E21" s="1">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
       <c r="C22" s="1">
         <v>46075</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="E22" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
       <c r="C23" s="1">
         <v>46076</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="E23" s="1">
+        <v>46104</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
       <c r="C24" s="1">
         <v>46077</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="E24" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
       <c r="C25" s="1">
         <v>46078</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="E25" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
       <c r="C26" s="1">
         <v>46079</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
       <c r="C27" s="1">
         <v>46080</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="E27" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19048,21 +19132,42 @@
       <c r="C28" s="1">
         <v>46081</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="E28" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="E29" s="1">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="E30" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
+      <c r="E31" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>17.5</v>
+      </c>
+      <c r="E32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -15953,9 +15953,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15965,15 +15965,22 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -15992,15 +15999,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -18726,10 +18726,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="5"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1">
         <v>46023</v>
       </c>
@@ -18739,8 +18739,14 @@
       <c r="E1" s="1">
         <v>46082</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1">
+        <v>46113</v>
+      </c>
+      <c r="H1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>46024</v>
       </c>
@@ -18756,8 +18762,14 @@
       <c r="F2">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>46025</v>
       </c>
@@ -18773,8 +18785,11 @@
       <c r="F3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>46026</v>
       </c>
@@ -18790,8 +18805,11 @@
       <c r="F4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>46027</v>
       </c>
@@ -18807,8 +18825,11 @@
       <c r="E5" s="1">
         <v>46086</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>46028</v>
       </c>
@@ -18827,8 +18848,11 @@
       <c r="F6">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>46029</v>
       </c>
@@ -18847,8 +18871,14 @@
       <c r="F7">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="1">
+        <v>46119</v>
+      </c>
+      <c r="H7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>46030</v>
       </c>
@@ -18862,10 +18892,13 @@
         <v>46089</v>
       </c>
       <c r="F8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>46031</v>
       </c>
@@ -18884,8 +18917,11 @@
       <c r="F9">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>46032</v>
       </c>
@@ -18898,8 +18934,11 @@
       <c r="E10" s="1">
         <v>46091</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>46033</v>
       </c>
@@ -18915,8 +18954,11 @@
       <c r="F11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>46034</v>
       </c>
@@ -18929,8 +18971,11 @@
       <c r="E12" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>46035</v>
       </c>
@@ -18943,8 +18988,11 @@
       <c r="E13" s="1">
         <v>46094</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>46036</v>
       </c>
@@ -18957,8 +19005,11 @@
       <c r="F14">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>46037</v>
       </c>
@@ -18968,8 +19019,11 @@
       <c r="E15" s="1">
         <v>46096</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>46038</v>
       </c>
@@ -18982,8 +19036,11 @@
       <c r="F16">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
@@ -18996,8 +19053,11 @@
       <c r="F17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
@@ -19010,8 +19070,11 @@
       <c r="F18">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
@@ -19024,8 +19087,11 @@
       <c r="F19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -19035,8 +19101,11 @@
       <c r="E20" s="1">
         <v>46101</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -19049,8 +19118,11 @@
       <c r="E21" s="1">
         <v>46102</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -19060,8 +19132,11 @@
       <c r="E22" s="1">
         <v>46103</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
@@ -19074,8 +19149,11 @@
       <c r="F23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
@@ -19085,8 +19163,11 @@
       <c r="E24" s="1">
         <v>46105</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
@@ -19096,8 +19177,11 @@
       <c r="E25" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -19110,8 +19194,11 @@
       <c r="E26" s="1">
         <v>46107</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
@@ -19121,8 +19208,11 @@
       <c r="E27" s="1">
         <v>46108</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19135,32 +19225,45 @@
       <c r="E28" s="1">
         <v>46109</v>
       </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
       <c r="E29" s="1">
         <v>46110</v>
       </c>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
       <c r="E30" s="1">
         <v>46111</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
       <c r="E31" s="1">
         <v>46112</v>
       </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="F31">
+        <v>2.5</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="B32">
         <v>8</v>
       </c>
@@ -19168,6 +19271,10 @@
         <v>17.5</v>
       </c>
       <c r="E32" s="1"/>
+      <c r="F32">
+        <v>35</v>
+      </c>
+      <c r="G32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
+    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -15959,12 +15959,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF212121"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -15974,7 +15968,20 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Chilanka"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -15982,13 +15989,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3" tint="-0.25"/>
-      <name val="Chilanka"/>
       <charset val="134"/>
     </font>
     <font>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="工时记录" sheetId="12" state="hidden" r:id="rId9"/>
     <sheet name="临时截图" sheetId="17" r:id="rId10"/>
     <sheet name="设置restful xdebug" sheetId="20" r:id="rId11"/>
-    <sheet name="2025月进度" sheetId="21" r:id="rId12"/>
+    <sheet name="2025月进度" sheetId="21" state="hidden" r:id="rId12"/>
     <sheet name="2026月进度" sheetId="22" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -15953,17 +15953,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -15975,8 +15987,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15986,23 +15998,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
   </fonts>
   <fills count="34">
@@ -19040,7 +19040,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
@@ -19073,8 +19073,11 @@
       <c r="G18" s="1">
         <v>46130</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
@@ -19091,7 +19094,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -19104,8 +19107,11 @@
       <c r="G20" s="1">
         <v>46132</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -19121,8 +19127,11 @@
       <c r="G21" s="1">
         <v>46133</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -19136,7 +19145,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
@@ -19152,8 +19161,11 @@
       <c r="G23" s="1">
         <v>46135</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
@@ -19166,8 +19178,11 @@
       <c r="G24" s="1">
         <v>46136</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
@@ -19180,8 +19195,11 @@
       <c r="G25" s="1">
         <v>46137</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -19198,7 +19216,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
@@ -19212,7 +19230,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19228,8 +19246,11 @@
       <c r="G28" s="1">
         <v>46140</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
@@ -19240,7 +19261,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
@@ -19251,7 +19272,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
@@ -19263,7 +19284,7 @@
       </c>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:8">
       <c r="B32">
         <v>8</v>
       </c>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
+    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -15953,19 +15953,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="AR PL UKai CN"/>
@@ -15980,15 +15967,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3" tint="-0.25"/>
-      <name val="Chilanka"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Chilanka"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15998,11 +15999,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="503">
   <si>
     <t>MRO - 产品清单页面增加到货数和到货率统计</t>
   </si>
@@ -15696,6 +15696,9 @@
   </si>
   <si>
     <t>10083  [袁鹏峰]-PA：新品流程追踪，更换数据源</t>
+  </si>
+  <si>
+    <t>总计</t>
   </si>
 </sst>
 </file>
@@ -15953,9 +15956,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="AR PL UKai CN"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="-0.25"/>
+      <name val="Chilanka"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15965,10 +15988,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
     <font>
@@ -15981,25 +16003,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3" tint="-0.25"/>
-      <name val="Chilanka"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF212121"/>
-      <name val="AR PL UKai CN"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
@@ -18726,10 +18729,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="7"/>
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1">
         <v>46023</v>
       </c>
@@ -18745,8 +18748,11 @@
       <c r="H1">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>46024</v>
       </c>
@@ -18768,8 +18774,11 @@
       <c r="H2">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>46025</v>
       </c>
@@ -18788,8 +18797,11 @@
       <c r="G3" s="1">
         <v>46115</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>46026</v>
       </c>
@@ -18808,8 +18820,11 @@
       <c r="G4" s="1">
         <v>46116</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>46027</v>
       </c>
@@ -18828,8 +18843,11 @@
       <c r="G5" s="1">
         <v>46117</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>46028</v>
       </c>
@@ -18851,8 +18869,11 @@
       <c r="G6" s="1">
         <v>46118</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>46029</v>
       </c>
@@ -18877,8 +18898,11 @@
       <c r="H7">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>46030</v>
       </c>
@@ -18897,8 +18921,11 @@
       <c r="G8" s="1">
         <v>46120</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>46031</v>
       </c>
@@ -18920,8 +18947,11 @@
       <c r="G9" s="1">
         <v>46121</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="1">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>46032</v>
       </c>
@@ -18937,8 +18967,11 @@
       <c r="G10" s="1">
         <v>46122</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>46033</v>
       </c>
@@ -18957,8 +18990,14 @@
       <c r="G11" s="1">
         <v>46123</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="1">
+        <v>46153</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>46034</v>
       </c>
@@ -18974,8 +19013,11 @@
       <c r="G12" s="1">
         <v>46124</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="1">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>46035</v>
       </c>
@@ -18991,8 +19033,14 @@
       <c r="G13" s="1">
         <v>46125</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="1">
+        <v>46155</v>
+      </c>
+      <c r="J13">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>46036</v>
       </c>
@@ -19008,8 +19056,11 @@
       <c r="G14" s="1">
         <v>46126</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>46037</v>
       </c>
@@ -19022,8 +19073,11 @@
       <c r="G15" s="1">
         <v>46127</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>46038</v>
       </c>
@@ -19039,8 +19093,11 @@
       <c r="G16" s="1">
         <v>46128</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
@@ -19056,8 +19113,11 @@
       <c r="G17" s="1">
         <v>46129</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="1">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
@@ -19076,8 +19136,11 @@
       <c r="H18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
@@ -19093,8 +19156,14 @@
       <c r="G19" s="1">
         <v>46131</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="1">
+        <v>46161</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -19110,8 +19179,14 @@
       <c r="H20">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="1">
+        <v>46162</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -19130,8 +19205,14 @@
       <c r="H21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="1">
+        <v>46163</v>
+      </c>
+      <c r="J21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -19144,8 +19225,11 @@
       <c r="G22" s="1">
         <v>46134</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="1">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
@@ -19164,8 +19248,11 @@
       <c r="H23">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="1">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
@@ -19181,8 +19268,11 @@
       <c r="H24">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
@@ -19198,8 +19288,14 @@
       <c r="H25">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" s="1">
+        <v>46167</v>
+      </c>
+      <c r="J25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -19215,8 +19311,11 @@
       <c r="G26" s="1">
         <v>46138</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
@@ -19229,8 +19328,11 @@
       <c r="G27" s="1">
         <v>46139</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19249,8 +19351,11 @@
       <c r="H28">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
@@ -19260,8 +19365,11 @@
       <c r="G29" s="1">
         <v>46141</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="I29" s="1">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
@@ -19271,8 +19379,11 @@
       <c r="G30" s="1">
         <v>46142</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
@@ -19283,8 +19394,14 @@
         <v>2.5</v>
       </c>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>502</v>
+      </c>
       <c r="B32">
         <v>8</v>
       </c>
@@ -19296,6 +19413,10 @@
         <v>35</v>
       </c>
       <c r="G32" s="1"/>
+      <c r="H32">
+        <v>19</v>
+      </c>
+      <c r="I32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -15956,14 +15956,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF212121"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
@@ -15979,18 +15991,6 @@
       <sz val="11"/>
       <color theme="3" tint="-0.25"/>
       <name val="Chilanka"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
     <font>
@@ -18729,10 +18729,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1">
         <v>46023</v>
       </c>
@@ -18751,8 +18751,14 @@
       <c r="I1" s="1">
         <v>46143</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1">
+        <v>46174</v>
+      </c>
+      <c r="L1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>46024</v>
       </c>
@@ -18777,8 +18783,14 @@
       <c r="I2" s="1">
         <v>46144</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="1">
+        <v>46175</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>46025</v>
       </c>
@@ -18800,8 +18812,14 @@
       <c r="I3" s="1">
         <v>46145</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="1">
+        <v>46176</v>
+      </c>
+      <c r="L3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>46026</v>
       </c>
@@ -18823,8 +18841,14 @@
       <c r="I4" s="1">
         <v>46146</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="1">
+        <v>46177</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>46027</v>
       </c>
@@ -18846,8 +18870,14 @@
       <c r="I5" s="1">
         <v>46147</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="1">
+        <v>46178</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>46028</v>
       </c>
@@ -18872,8 +18902,14 @@
       <c r="I6" s="1">
         <v>46148</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="1">
+        <v>46179</v>
+      </c>
+      <c r="L6">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>46029</v>
       </c>
@@ -18901,8 +18937,14 @@
       <c r="I7" s="1">
         <v>46149</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="1">
+        <v>46180</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>46030</v>
       </c>
@@ -18924,8 +18966,11 @@
       <c r="I8" s="1">
         <v>46150</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="1">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>46031</v>
       </c>
@@ -18950,8 +18995,11 @@
       <c r="I9" s="1">
         <v>46151</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>46032</v>
       </c>
@@ -18970,8 +19018,11 @@
       <c r="I10" s="1">
         <v>46152</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="1">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>46033</v>
       </c>
@@ -18996,8 +19047,11 @@
       <c r="J11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>46034</v>
       </c>
@@ -19016,8 +19070,11 @@
       <c r="I12" s="1">
         <v>46154</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="1">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>46035</v>
       </c>
@@ -19039,8 +19096,11 @@
       <c r="J13">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="1">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <v>46036</v>
       </c>
@@ -19059,8 +19119,11 @@
       <c r="I14" s="1">
         <v>46156</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1">
         <v>46037</v>
       </c>
@@ -19076,8 +19139,11 @@
       <c r="I15" s="1">
         <v>46157</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1">
         <v>46038</v>
       </c>
@@ -19096,8 +19162,11 @@
       <c r="I16" s="1">
         <v>46158</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16" s="1">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
@@ -19116,8 +19185,11 @@
       <c r="I17" s="1">
         <v>46159</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17" s="1">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
@@ -19139,8 +19211,11 @@
       <c r="I18" s="1">
         <v>46160</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
@@ -19162,8 +19237,11 @@
       <c r="J19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -19185,8 +19263,11 @@
       <c r="J20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -19211,8 +19292,11 @@
       <c r="J21">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -19228,8 +19312,11 @@
       <c r="I22" s="1">
         <v>46164</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
@@ -19251,8 +19338,11 @@
       <c r="I23" s="1">
         <v>46165</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
@@ -19271,8 +19361,11 @@
       <c r="I24" s="1">
         <v>46166</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
@@ -19294,8 +19387,11 @@
       <c r="J25">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -19314,8 +19410,11 @@
       <c r="I26" s="1">
         <v>46168</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
@@ -19331,8 +19430,14 @@
       <c r="I27" s="1">
         <v>46169</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27">
+        <v>2.5</v>
+      </c>
+      <c r="K27" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19354,8 +19459,14 @@
       <c r="I28" s="1">
         <v>46170</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
@@ -19368,8 +19479,11 @@
       <c r="I29" s="1">
         <v>46171</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29" s="1">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
@@ -19382,8 +19496,14 @@
       <c r="I30" s="1">
         <v>46172</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="J30">
+        <v>6</v>
+      </c>
+      <c r="K30" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
@@ -19397,8 +19517,9 @@
       <c r="I31" s="1">
         <v>46173</v>
       </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
         <v>502</v>
       </c>
@@ -19417,6 +19538,9 @@
         <v>19</v>
       </c>
       <c r="I32" s="1"/>
+      <c r="J32">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
+++ b/pa-temp-fix-system.com/beifen/工作日志记录表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31770" windowHeight="17970" firstSheet="1" activeTab="12"/>
+    <workbookView windowWidth="28000" windowHeight="18200" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="分支管理" sheetId="9" state="hidden" r:id="rId1"/>
@@ -15956,6 +15956,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="AR PL UKai CN"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF212121"/>
       <name val="AR PL UKai CN"/>
@@ -15968,10 +15981,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -15982,29 +16003,8 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3" tint="-0.25"/>
       <name val="Chilanka"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="AR PL UKai CN"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -16662,8 +16662,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3572510" y="46523275"/>
-          <a:ext cx="6348095" cy="2533650"/>
+          <a:off x="3096260" y="44024550"/>
+          <a:ext cx="5625465" cy="2286000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16704,8 +16704,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3639185" y="82804000"/>
-          <a:ext cx="2030730" cy="1181100"/>
+          <a:off x="3162935" y="77903070"/>
+          <a:ext cx="2030730" cy="1156335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16746,8 +16746,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3572510" y="116332000"/>
-          <a:ext cx="14366240" cy="4124325"/>
+          <a:off x="3096260" y="109799120"/>
+          <a:ext cx="12867640" cy="3705860"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16792,8 +16792,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="933450" y="42376725"/>
-          <a:ext cx="304800" cy="304800"/>
+          <a:off x="808990" y="40416480"/>
+          <a:ext cx="304800" cy="280035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16839,8 +16839,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="3992245"/>
-          <a:ext cx="6172200" cy="5904865"/>
+          <a:off x="594360" y="3733165"/>
+          <a:ext cx="5349240" cy="5508625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16882,7 +16882,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="505460" y="86360"/>
-          <a:ext cx="18402300" cy="7391400"/>
+          <a:ext cx="15933420" cy="6903720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16928,8 +16928,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="228600"/>
-          <a:ext cx="14745970" cy="11896725"/>
+          <a:off x="9525" y="213360"/>
+          <a:ext cx="12812395" cy="11104245"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16970,8 +16970,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="14173200"/>
-          <a:ext cx="7413625" cy="7477125"/>
+          <a:off x="0" y="13228320"/>
+          <a:ext cx="6492875" cy="6989445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -16994,8 +16994,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>5715</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17012,8 +17012,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="22860000"/>
-          <a:ext cx="6908800" cy="8677275"/>
+          <a:off x="0" y="21336000"/>
+          <a:ext cx="5988050" cy="8113395"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17054,8 +17054,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6889750" y="15192375"/>
-          <a:ext cx="8404860" cy="6677025"/>
+          <a:off x="5988050" y="14186535"/>
+          <a:ext cx="7280910" cy="6235065"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17078,8 +17078,8 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>164</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>5715</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17096,8 +17096,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="32689800"/>
-          <a:ext cx="11558905" cy="5019675"/>
+          <a:off x="0" y="30510480"/>
+          <a:ext cx="10085705" cy="4699635"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17138,8 +17138,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="38404800"/>
-          <a:ext cx="6908800" cy="3286125"/>
+          <a:off x="0" y="35844480"/>
+          <a:ext cx="5988050" cy="3072765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17443,7 +17443,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A15:C18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="42.25" customWidth="1"/>
     <col min="2" max="2" width="81.25" customWidth="1"/>
@@ -17493,7 +17493,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XFD1048576"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <mergeCells count="1">
     <mergeCell ref="A1:XFD1048576"/>
@@ -17509,7 +17509,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.06666666666667" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9.06730769230769" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -17521,7 +17521,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.625" customWidth="1"/>
     <col min="5" max="5" width="17.375" customWidth="1"/>
@@ -18730,7 +18730,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1">
@@ -18998,6 +18998,9 @@
       <c r="K9" s="1">
         <v>46182</v>
       </c>
+      <c r="L9">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1">
@@ -19021,6 +19024,9 @@
       <c r="K10" s="1">
         <v>46183</v>
       </c>
+      <c r="L10">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1">
@@ -19099,6 +19105,9 @@
       <c r="K13" s="1">
         <v>46186</v>
       </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="1">
@@ -19122,6 +19131,9 @@
       <c r="K14" s="1">
         <v>46187</v>
       </c>
+      <c r="L14">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1">
@@ -19166,7 +19178,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>46039</v>
       </c>
@@ -19188,8 +19200,11 @@
       <c r="K17" s="1">
         <v>46190</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>46040</v>
       </c>
@@ -19215,7 +19230,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>46041</v>
       </c>
@@ -19240,8 +19255,11 @@
       <c r="K19" s="1">
         <v>46192</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>46042</v>
       </c>
@@ -19267,7 +19285,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>46043</v>
       </c>
@@ -19296,7 +19314,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <v>46044</v>
       </c>
@@ -19315,8 +19333,11 @@
       <c r="K22" s="1">
         <v>46195</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="1">
         <v>46045</v>
       </c>
@@ -19341,8 +19362,11 @@
       <c r="K23" s="1">
         <v>46196</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="1">
         <v>46046</v>
       </c>
@@ -19364,8 +19388,11 @@
       <c r="K24" s="1">
         <v>46197</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="1">
         <v>46047</v>
       </c>
@@ -19390,8 +19417,11 @@
       <c r="K25" s="1">
         <v>46198</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="1">
         <v>46048</v>
       </c>
@@ -19413,8 +19443,11 @@
       <c r="K26" s="1">
         <v>46199</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="1">
         <v>46049</v>
       </c>
@@ -19437,7 +19470,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28" s="1">
         <v>46050</v>
       </c>
@@ -19466,7 +19499,7 @@
         <v>46201</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29" s="1">
         <v>46051</v>
       </c>
@@ -19482,8 +19515,11 @@
       <c r="K29" s="1">
         <v>46202</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="1">
         <v>46052</v>
       </c>
@@ -19503,7 +19539,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:12">
       <c r="A31" s="1">
         <v>46053</v>
       </c>
@@ -19519,7 +19555,7 @@
       </c>
       <c r="K31" s="1"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>502</v>
       </c>
@@ -19540,6 +19576,9 @@
       <c r="I32" s="1"/>
       <c r="J32">
         <v>22</v>
+      </c>
+      <c r="L32">
+        <v>51.5</v>
       </c>
     </row>
   </sheetData>
@@ -19552,18 +19591,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M316"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="22.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.1333333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.1346153846154" style="3" customWidth="1"/>
     <col min="3" max="3" width="71.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="58.3833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="58.3846153846154" style="3" customWidth="1"/>
     <col min="5" max="6" width="9" style="3"/>
     <col min="7" max="7" width="66.625" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" ht="17" spans="2:7">
       <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
@@ -19571,7 +19610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" ht="17" spans="2:7">
       <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
@@ -19579,7 +19618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="37.5" spans="2:7">
+    <row r="3" ht="34" spans="2:7">
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
@@ -19587,7 +19626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" ht="17" spans="2:7">
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
@@ -19595,7 +19634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" ht="17" spans="2:7">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -19603,7 +19642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" ht="17" spans="2:7">
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -19611,7 +19650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" ht="17" spans="2:7">
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
@@ -19633,7 +19672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" ht="17" spans="2:7">
       <c r="B11" s="3" t="s">
         <v>27</v>
       </c>
@@ -19641,7 +19680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" ht="131.25" spans="2:7">
+    <row r="12" ht="135" spans="2:7">
       <c r="B12" s="3" t="s">
         <v>29</v>
       </c>
@@ -19652,7 +19691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="2:7">
+    <row r="15" ht="17" spans="2:7">
       <c r="B15" s="3" t="s">
         <v>32</v>
       </c>
@@ -19660,7 +19699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" ht="56.25" spans="1:4">
+    <row r="18" ht="51" spans="1:4">
       <c r="B18" s="3" t="s">
         <v>33</v>
       </c>
@@ -19668,7 +19707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" ht="17" spans="1:4">
       <c r="B21" s="3" t="s">
         <v>35</v>
       </c>
@@ -19676,7 +19715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" ht="17" spans="1:4">
       <c r="B22" s="3" t="s">
         <v>37</v>
       </c>
@@ -19684,12 +19723,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" ht="17" spans="1:4">
       <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" ht="17" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -19705,7 +19744,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" ht="150" spans="1:4">
+    <row r="26" ht="135" spans="1:4">
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
@@ -19749,7 +19788,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" ht="56.25" spans="2:4">
+    <row r="36" ht="51" spans="2:4">
       <c r="B36" s="3" t="s">
         <v>51</v>
       </c>
@@ -19757,7 +19796,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" ht="17" spans="2:4">
       <c r="B39" s="3" t="s">
         <v>53</v>
       </c>
@@ -19779,7 +19818,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" ht="313.5" spans="2:4">
+    <row r="48" ht="336" spans="2:4">
       <c r="B48" s="3" t="s">
         <v>56</v>
       </c>
@@ -19804,7 +19843,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" ht="17" spans="2:13">
       <c r="B51" s="3" t="s">
         <v>63</v>
       </c>
@@ -19812,7 +19851,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" ht="17" spans="2:13">
       <c r="B52" s="3" t="s">
         <v>65</v>
       </c>
@@ -19820,12 +19859,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" ht="17" spans="2:13">
       <c r="B55" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" ht="17" spans="2:13">
       <c r="B56" s="3" t="s">
         <v>68</v>
       </c>
@@ -19833,7 +19872,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" ht="17" spans="2:13">
       <c r="B57" s="3" t="s">
         <v>70</v>
       </c>
@@ -19891,12 +19930,12 @@
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
     </row>
-    <row r="71" spans="2:4">
+    <row r="71" ht="17" spans="2:4">
       <c r="B71" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="72" ht="37.5" spans="2:4">
+    <row r="72" ht="34" spans="2:4">
       <c r="B72" s="3" t="s">
         <v>74</v>
       </c>
@@ -19904,7 +19943,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="2:4">
+    <row r="74" ht="17" spans="2:4">
       <c r="B74" s="3" t="s">
         <v>76</v>
       </c>
@@ -19915,7 +19954,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="2:4">
+    <row r="75" ht="17" spans="2:4">
       <c r="B75" s="3" t="s">
         <v>79</v>
       </c>
@@ -19924,7 +19963,7 @@
       </c>
       <c r="D75" s="29"/>
     </row>
-    <row r="76" spans="2:4">
+    <row r="76" ht="17" spans="2:4">
       <c r="B76" s="3" t="s">
         <v>81</v>
       </c>
@@ -19933,7 +19972,7 @@
       </c>
       <c r="D76" s="29"/>
     </row>
-    <row r="81" spans="2:3">
+    <row r="81" ht="17" spans="2:3">
       <c r="B81" s="3" t="s">
         <v>83</v>
       </c>
@@ -19941,7 +19980,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="2:3">
+    <row r="83" ht="17" spans="2:3">
       <c r="B83" s="3" t="s">
         <v>85</v>
       </c>
@@ -19949,7 +19988,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="2:3">
+    <row r="84" ht="17" spans="2:3">
       <c r="B84" s="3" t="s">
         <v>87</v>
       </c>
@@ -19957,7 +19996,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="2:3">
+    <row r="86" ht="17" spans="2:3">
       <c r="B86" s="3" t="s">
         <v>89</v>
       </c>
@@ -19967,12 +20006,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="2:3">
+    <row r="88" ht="17" spans="2:3">
       <c r="B88" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" spans="2:3">
+    <row r="92" ht="17" spans="2:3">
       <c r="B92" s="3" t="s">
         <v>92</v>
       </c>
@@ -19980,7 +20019,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" ht="56.25" spans="2:3">
+    <row r="95" ht="51" spans="2:3">
       <c r="B95" s="3" t="s">
         <v>94</v>
       </c>
@@ -19998,12 +20037,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="102" spans="2:3">
+    <row r="102" ht="17" spans="2:3">
       <c r="B102" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="2:3">
+    <row r="105" ht="17" spans="2:3">
       <c r="B105" s="3" t="s">
         <v>99</v>
       </c>
@@ -20011,12 +20050,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="109" ht="112.5" spans="2:3">
+    <row r="109" ht="118" spans="2:3">
       <c r="B109" s="9" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="110" spans="2:3">
+    <row r="110" ht="17" spans="2:3">
       <c r="B110" s="3" t="s">
         <v>102</v>
       </c>
@@ -20024,17 +20063,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="126" spans="2:2">
+    <row r="126" ht="17" spans="2:2">
       <c r="B126" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="128" spans="2:2">
+    <row r="128" ht="17" spans="2:2">
       <c r="B128" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="130" spans="2:3">
+    <row r="130" ht="17" spans="2:3">
       <c r="B130" s="3" t="s">
         <v>106</v>
       </c>
@@ -20049,17 +20088,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="136" spans="2:3">
+    <row r="136" ht="17" spans="2:3">
       <c r="B136" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="138" spans="2:3">
+    <row r="138" ht="17" spans="2:3">
       <c r="B138" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="140" spans="2:3">
+    <row r="140" ht="17" spans="2:3">
       <c r="B140" s="3" t="s">
         <v>111</v>
       </c>
@@ -20069,7 +20108,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="144" spans="2:3">
+    <row r="144" ht="17" spans="2:3">
       <c r="B144" s="3" t="s">
         <v>113</v>
       </c>
@@ -20077,7 +20116,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" ht="17" spans="1:3">
       <c r="B147" s="3" t="s">
         <v>115</v>
       </c>
@@ -20085,7 +20124,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" ht="17" spans="1:3">
       <c r="B148" s="3" t="s">
         <v>117</v>
       </c>
@@ -20101,7 +20140,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" ht="17" spans="1:3">
       <c r="B150" s="29"/>
       <c r="C150" s="3" t="s">
         <v>121</v>
@@ -20113,7 +20152,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" ht="17" spans="1:3">
       <c r="B154" s="3" t="s">
         <v>123</v>
       </c>
@@ -20121,7 +20160,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" ht="17" spans="1:3">
       <c r="A157" s="3" t="s">
         <v>125</v>
       </c>
@@ -20154,7 +20193,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="170" spans="2:3">
+    <row r="170" ht="17" spans="2:3">
       <c r="B170" s="3" t="s">
         <v>132</v>
       </c>
@@ -20162,7 +20201,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="171" spans="2:3">
+    <row r="171" ht="17" spans="2:3">
       <c r="B171" s="3" t="s">
         <v>134</v>
       </c>
@@ -20170,7 +20209,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="172" spans="2:3">
+    <row r="172" ht="17" spans="2:3">
       <c r="B172" s="3" t="s">
         <v>136</v>
       </c>
@@ -20178,7 +20217,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="173" spans="2:3">
+    <row r="173" ht="17" spans="2:3">
       <c r="B173" s="3" t="s">
         <v>138</v>
       </c>
@@ -20186,7 +20225,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="174" spans="2:3">
+    <row r="174" ht="17" spans="2:3">
       <c r="B174" s="3" t="s">
         <v>140</v>
       </c>
@@ -20202,12 +20241,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="183" spans="2:3">
+    <row r="183" ht="17" spans="2:3">
       <c r="B183" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="185" spans="2:3">
+    <row r="185" ht="17" spans="2:3">
       <c r="B185" s="3" t="s">
         <v>144</v>
       </c>
@@ -20222,7 +20261,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="190" spans="2:3">
+    <row r="190" ht="17" spans="2:3">
       <c r="B190" s="3" t="s">
         <v>147</v>
       </c>
@@ -20257,12 +20296,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="202" spans="2:3">
+    <row r="202" ht="17" spans="2:3">
       <c r="B202" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="203" spans="2:3">
+    <row r="203" ht="17" spans="2:3">
       <c r="B203" s="3" t="s">
         <v>155</v>
       </c>
@@ -20272,12 +20311,12 @@
         <v>156</v>
       </c>
     </row>
-    <row r="207" spans="2:3">
+    <row r="207" ht="17" spans="2:3">
       <c r="C207" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="209" spans="2:7">
+    <row r="209" ht="17" spans="2:7">
       <c r="B209" s="3" t="s">
         <v>158</v>
       </c>
@@ -20287,17 +20326,17 @@
         <v>159</v>
       </c>
     </row>
-    <row r="213" spans="2:7">
+    <row r="213" ht="17" spans="2:7">
       <c r="B213" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="214" spans="2:7">
+    <row r="214" ht="17" spans="2:7">
       <c r="B214" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="215" ht="158.25" spans="2:7">
+    <row r="215" ht="168" spans="2:7">
       <c r="B215" s="9" t="s">
         <v>162</v>
       </c>
@@ -20310,12 +20349,12 @@
         <v>164</v>
       </c>
     </row>
-    <row r="218" spans="2:7">
+    <row r="218" ht="17" spans="2:7">
       <c r="B218" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="221" ht="243.75" spans="2:7">
+    <row r="221" ht="252" spans="2:7">
       <c r="B221" s="19" t="s">
         <v>166</v>
       </c>
@@ -20340,12 +20379,12 @@
         <v>172</v>
       </c>
     </row>
-    <row r="226" ht="131.25" spans="1:2">
+    <row r="226" ht="135" spans="1:2">
       <c r="B226" s="9" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="229" ht="37.5" spans="1:2">
+    <row r="229" ht="34" spans="1:2">
       <c r="A229" s="32" t="s">
         <v>174</v>
       </c>
@@ -20353,7 +20392,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" ht="17" spans="1:2">
       <c r="A234" s="3" t="s">
         <v>176</v>
       </c>
@@ -20366,7 +20405,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" ht="17" spans="1:4">
       <c r="A243" s="3" t="s">
         <v>179</v>
       </c>
@@ -20385,7 +20424,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" ht="17" spans="1:4">
       <c r="A251" s="3" t="s">
         <v>183</v>
       </c>
@@ -20393,7 +20432,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" ht="17" spans="1:4">
       <c r="B253" s="3" t="s">
         <v>185</v>
       </c>
@@ -20406,12 +20445,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="258" ht="313.5" spans="1:4">
+    <row r="258" ht="320" spans="1:4">
       <c r="B258" s="9" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" ht="17" spans="1:4">
       <c r="A261" s="3" t="s">
         <v>189</v>
       </c>
@@ -20422,12 +20461,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" ht="17" spans="1:4">
       <c r="B263" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="264" ht="56.25" spans="1:4">
+    <row r="264" ht="51" spans="1:4">
       <c r="A264" s="3" t="s">
         <v>193</v>
       </c>
@@ -20435,12 +20474,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" ht="17" spans="1:4">
       <c r="C266" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="269" ht="356.25" spans="1:4">
+    <row r="269" ht="320" spans="1:4">
       <c r="A269" s="3" t="s">
         <v>196</v>
       </c>
@@ -20459,7 +20498,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" ht="17" spans="1:3">
       <c r="A279" s="3" t="s">
         <v>201</v>
       </c>
@@ -20467,7 +20506,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" ht="17" spans="1:3">
       <c r="A280" s="3" t="s">
         <v>203</v>
       </c>
@@ -20475,12 +20514,12 @@
         <v>204</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" ht="17" spans="1:3">
       <c r="B283" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="306" spans="2:3">
+    <row r="306" ht="17" spans="2:3">
       <c r="B306" s="3" t="s">
         <v>206</v>
       </c>
@@ -20490,19 +20529,19 @@
         <v>207</v>
       </c>
     </row>
-    <row r="308" spans="2:3">
+    <row r="308" ht="17" spans="2:3">
       <c r="B308" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C308" s="28"/>
     </row>
-    <row r="309" spans="2:3">
+    <row r="309" ht="17" spans="2:3">
       <c r="B309" s="3" t="s">
         <v>209</v>
       </c>
       <c r="C309" s="28"/>
     </row>
-    <row r="310" spans="2:3">
+    <row r="310" ht="17" spans="2:3">
       <c r="B310" s="3" t="s">
         <v>210</v>
       </c>
@@ -20520,7 +20559,7 @@
     <row r="314" spans="2:3">
       <c r="C314" s="28"/>
     </row>
-    <row r="316" spans="2:3">
+    <row r="316" ht="17" spans="2:3">
       <c r="B316" s="3" t="s">
         <v>211</v>
       </c>
@@ -20556,18 +20595,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O134"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="36.15" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.525" style="3" customWidth="1"/>
-    <col min="4" max="4" width="76.6166666666667" style="3" customWidth="1"/>
+    <col min="2" max="2" width="36.1538461538462" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.5288461538462" style="3" customWidth="1"/>
+    <col min="4" max="4" width="76.6153846153846" style="3" customWidth="1"/>
     <col min="5" max="5" width="17.625" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="62.65" style="3" customWidth="1"/>
+    <col min="7" max="7" width="62.6538461538462" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" ht="17" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>212</v>
       </c>
@@ -20836,7 +20875,7 @@
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" ht="17" spans="1:15">
       <c r="A15" s="3">
         <v>8001</v>
       </c>
@@ -20873,7 +20912,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" ht="17" spans="1:12">
       <c r="A18" s="3">
         <v>7000</v>
       </c>
@@ -20890,7 +20929,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" ht="17" spans="1:12">
       <c r="B20" s="3" t="s">
         <v>251</v>
       </c>
@@ -20937,7 +20976,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="28" ht="37.5" spans="1:12">
+    <row r="28" ht="51" spans="1:12">
       <c r="B28" s="9" t="s">
         <v>258</v>
       </c>
@@ -20953,7 +20992,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="30" ht="93.75" spans="1:12">
+    <row r="30" ht="101" spans="1:12">
       <c r="B30" s="9" t="s">
         <v>261</v>
       </c>
@@ -20966,7 +21005,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" ht="17" spans="1:12">
       <c r="D32" s="3" t="s">
         <v>264</v>
       </c>
@@ -20979,7 +21018,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="34" ht="75" spans="2:7">
+    <row r="34" ht="84" spans="2:7">
       <c r="B34" s="3" t="s">
         <v>267</v>
       </c>
@@ -20996,12 +21035,12 @@
       </c>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" ht="93.75" spans="2:7">
+    <row r="37" ht="84" spans="2:7">
       <c r="G37" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="38" spans="2:7">
+    <row r="38" ht="17" spans="2:7">
       <c r="B38" s="3" t="s">
         <v>271</v>
       </c>
@@ -21021,7 +21060,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="43" spans="2:7">
+    <row r="43" ht="17" spans="2:7">
       <c r="B43" s="12" t="s">
         <v>275</v>
       </c>
@@ -21033,7 +21072,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="44" spans="2:7">
+    <row r="44" ht="17" spans="2:7">
       <c r="B44" s="12" t="s">
         <v>278</v>
       </c>
@@ -21047,22 +21086,22 @@
         <v>280</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" ht="17" spans="2:7">
       <c r="B47" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
+    <row r="48" ht="17" spans="2:7">
       <c r="B48" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="49" ht="75" spans="1:4">
+    <row r="49" ht="68" spans="1:4">
       <c r="B49" s="9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" ht="17" spans="1:4">
       <c r="A50" s="3" t="s">
         <v>284</v>
       </c>
@@ -21073,17 +21112,17 @@
         <v>286</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" ht="17" spans="1:4">
       <c r="C51" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" ht="17" spans="1:4">
       <c r="C52" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" ht="17" spans="1:4">
       <c r="A53" s="3" t="s">
         <v>289</v>
       </c>
@@ -21094,7 +21133,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" ht="17" spans="1:4">
       <c r="C54" s="4" t="s">
         <v>292</v>
       </c>
@@ -21102,7 +21141,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" ht="17" spans="1:4">
       <c r="B55" s="9" t="s">
         <v>294</v>
       </c>
@@ -21190,7 +21229,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" ht="17" spans="1:4">
       <c r="A79" s="3" t="s">
         <v>303</v>
       </c>
@@ -21213,7 +21252,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="87" spans="2:4">
+    <row r="87" ht="17" spans="2:4">
       <c r="C87" s="3" t="s">
         <v>308</v>
       </c>
@@ -21226,7 +21265,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="94" ht="112.5" spans="2:4">
+    <row r="94" ht="118" spans="2:4">
       <c r="B94" s="9" t="s">
         <v>311</v>
       </c>
@@ -21234,7 +21273,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="97" ht="243" spans="2:4">
+    <row r="97" ht="252" spans="2:4">
       <c r="B97" s="9" t="s">
         <v>313</v>
       </c>
@@ -21245,7 +21284,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="98" ht="262.5" spans="2:4">
+    <row r="98" ht="286" spans="2:4">
       <c r="B98" s="9" t="s">
         <v>316</v>
       </c>
@@ -21253,7 +21292,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="101" spans="2:4">
+    <row r="101" ht="17" spans="2:4">
       <c r="B101" s="3" t="s">
         <v>318</v>
       </c>
@@ -21261,7 +21300,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="105" ht="393.75" spans="2:4">
+    <row r="105" ht="387" spans="2:4">
       <c r="C105" s="9" t="s">
         <v>320</v>
       </c>
@@ -21269,7 +21308,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="2:4">
+    <row r="109" ht="17" spans="2:4">
       <c r="B109" s="3" t="s">
         <v>322</v>
       </c>
@@ -21277,7 +21316,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="112" spans="2:4">
+    <row r="112" ht="17" spans="2:4">
       <c r="B112" s="21" t="s">
         <v>324</v>
       </c>
@@ -21336,12 +21375,12 @@
     <row r="126" spans="2:3">
       <c r="B126" s="22"/>
     </row>
-    <row r="128" spans="2:3">
+    <row r="128" ht="17" spans="2:3">
       <c r="B128" s="20" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="129" ht="300" spans="2:4">
+    <row r="129" ht="269" spans="2:4">
       <c r="B129" s="20" t="s">
         <v>328</v>
       </c>
@@ -21349,7 +21388,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="131" ht="110.25" spans="2:4">
+    <row r="131" ht="118" spans="2:4">
       <c r="B131" s="9" t="s">
         <v>330</v>
       </c>
@@ -21359,7 +21398,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="134" ht="225" spans="2:4">
+    <row r="134" ht="236" spans="2:4">
       <c r="C134" s="9" t="s">
         <v>332</v>
       </c>
@@ -21397,65 +21436,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="92.8" style="3" customWidth="1"/>
+    <col min="1" max="1" width="92.7980769230769" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="41" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" ht="17" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" ht="17" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" ht="17" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" ht="17" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" ht="17" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" ht="17" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" ht="17" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" ht="17" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" ht="17" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="14" ht="356.25" spans="1:3">
+    <row r="14" ht="320" spans="1:3">
       <c r="A14" s="9" t="s">
         <v>344</v>
       </c>
@@ -21463,17 +21502,17 @@
         <v>345</v>
       </c>
     </row>
-    <row r="17" ht="131.25" spans="1:1">
+    <row r="17" ht="118" spans="1:1">
       <c r="A17" s="9" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="19" ht="225" spans="1:1">
+    <row r="19" ht="202" spans="1:1">
       <c r="A19" s="9" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="21" ht="112.5" spans="1:1">
+    <row r="21" ht="101" spans="1:1">
       <c r="A21" s="9" t="s">
         <v>348</v>
       </c>
@@ -21488,7 +21527,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="29.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="142" style="3" customWidth="1"/>
@@ -21497,7 +21536,7 @@
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" ht="17" spans="1:4">
       <c r="A1" s="5" t="s">
         <v>349</v>
       </c>
@@ -21511,7 +21550,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" ht="17" spans="1:4">
       <c r="A2" s="10" t="s">
         <v>353</v>
       </c>
@@ -21522,7 +21561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" ht="17" spans="1:4">
       <c r="B3" s="3" t="s">
         <v>355</v>
       </c>
@@ -21530,7 +21569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" ht="17" spans="1:4">
       <c r="B4" s="3" t="s">
         <v>356</v>
       </c>
@@ -21538,7 +21577,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" ht="17" spans="1:4">
       <c r="B5" s="3" t="s">
         <v>357</v>
       </c>
@@ -21546,7 +21585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" ht="17" spans="1:4">
       <c r="B6" s="3" t="s">
         <v>358</v>
       </c>
@@ -21554,7 +21593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" ht="17" spans="1:4">
       <c r="B7" s="3" t="s">
         <v>359</v>
       </c>
@@ -21562,7 +21601,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" ht="17" spans="1:4">
       <c r="B8" s="3" t="s">
         <v>361</v>
       </c>
@@ -21585,7 +21624,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="36" style="3" customWidth="1"/>
     <col min="2" max="2" width="63.75" style="3" customWidth="1"/>
@@ -21595,7 +21634,7 @@
     <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" ht="17" spans="2:7">
       <c r="B1" s="3" t="s">
         <v>362</v>
       </c>
@@ -21609,7 +21648,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" ht="17" spans="2:7">
       <c r="B2" s="3" t="s">
         <v>366</v>
       </c>
@@ -21623,7 +21662,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" ht="17" spans="2:7">
       <c r="B3" s="3" t="s">
         <v>370</v>
       </c>
@@ -21651,7 +21690,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" ht="17" spans="2:7">
       <c r="B5" s="3" t="s">
         <v>378</v>
       </c>
@@ -21665,12 +21704,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="7" ht="37.5" spans="2:7">
+    <row r="7" ht="34" spans="2:7">
       <c r="B7" s="9" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" ht="17" spans="2:7">
       <c r="B10" s="7" t="s">
         <v>382</v>
       </c>
@@ -21678,7 +21717,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" ht="17" spans="2:7">
       <c r="B11" s="8" t="s">
         <v>384</v>
       </c>
@@ -21694,7 +21733,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" ht="17" spans="1:3">
       <c r="B18" s="3" t="s">
         <v>387</v>
       </c>
@@ -21702,7 +21741,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" ht="17" spans="1:3">
       <c r="B19" s="3" t="s">
         <v>389</v>
       </c>
@@ -21710,7 +21749,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" ht="17" spans="1:3">
       <c r="B20" s="3" t="s">
         <v>391</v>
       </c>
@@ -21718,7 +21757,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" ht="17" spans="1:3">
       <c r="B22" s="3" t="s">
         <v>393</v>
       </c>
@@ -21726,7 +21765,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" ht="17" spans="1:3">
       <c r="B23" s="3" t="s">
         <v>395</v>
       </c>
@@ -21734,7 +21773,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" ht="17" spans="1:3">
       <c r="A24" s="3" t="s">
         <v>397</v>
       </c>
@@ -21745,7 +21784,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" ht="17" spans="1:3">
       <c r="B25" s="3" t="s">
         <v>400</v>
       </c>
@@ -21753,7 +21792,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" ht="17" spans="1:3">
       <c r="B26" s="3" t="s">
         <v>402</v>
       </c>
@@ -21761,7 +21800,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" ht="17" spans="1:3">
       <c r="B27" s="3" t="s">
         <v>404</v>
       </c>
@@ -21769,7 +21808,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" ht="17" spans="1:3">
       <c r="B28" s="3" t="s">
         <v>406</v>
       </c>
@@ -21777,7 +21816,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" ht="17" spans="1:3">
       <c r="B29" s="3" t="s">
         <v>408</v>
       </c>
@@ -21785,7 +21824,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" ht="17" spans="1:3">
       <c r="B30" s="3" t="s">
         <v>410</v>
       </c>
@@ -21793,7 +21832,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" ht="17" spans="1:3">
       <c r="B31" s="3" t="s">
         <v>412</v>
       </c>
@@ -21801,7 +21840,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
+    <row r="34" ht="17" spans="2:3">
       <c r="B34" s="3" t="s">
         <v>414</v>
       </c>
@@ -21809,7 +21848,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="36" spans="2:3">
+    <row r="36" ht="17" spans="2:3">
       <c r="B36" s="3" t="s">
         <v>416</v>
       </c>
@@ -21817,7 +21856,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="38" spans="2:3">
+    <row r="38" ht="17" spans="2:3">
       <c r="B38" s="3" t="s">
         <v>418</v>
       </c>
@@ -21825,7 +21864,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="2:3">
+    <row r="40" ht="17" spans="2:3">
       <c r="B40" s="3" t="s">
         <v>420</v>
       </c>
@@ -21833,7 +21872,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="41" spans="2:3">
+    <row r="41" ht="17" spans="2:3">
       <c r="B41" s="3" t="s">
         <v>422</v>
       </c>
@@ -21841,7 +21880,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="42" spans="2:3">
+    <row r="42" ht="17" spans="2:3">
       <c r="B42" s="3" t="s">
         <v>424</v>
       </c>
@@ -21849,7 +21888,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="43" spans="2:3">
+    <row r="43" ht="17" spans="2:3">
       <c r="B43" s="3" t="s">
         <v>426</v>
       </c>
@@ -21857,12 +21896,12 @@
         <v>427</v>
       </c>
     </row>
-    <row r="45" spans="2:3">
+    <row r="45" ht="17" spans="2:3">
       <c r="B45" s="3" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="48" spans="2:3">
+    <row r="48" ht="17" spans="2:3">
       <c r="B48" s="3" t="s">
         <v>429</v>
       </c>
@@ -21870,7 +21909,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="49" spans="2:3">
+    <row r="49" ht="17" spans="2:3">
       <c r="B49" s="3" t="s">
         <v>431</v>
       </c>
@@ -21878,7 +21917,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="53" ht="56.25" spans="2:3">
+    <row r="53" ht="51" spans="2:3">
       <c r="B53" s="3" t="s">
         <v>433</v>
       </c>
@@ -21886,12 +21925,12 @@
         <v>434</v>
       </c>
     </row>
-    <row r="54" spans="2:3">
+    <row r="54" ht="17" spans="2:3">
       <c r="C54" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="56" spans="2:3">
+    <row r="56" ht="17" spans="2:3">
       <c r="B56" s="3" t="s">
         <v>436</v>
       </c>
@@ -21899,7 +21938,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="57" spans="2:3">
+    <row r="57" ht="17" spans="2:3">
       <c r="B57" s="3" t="s">
         <v>438</v>
       </c>
@@ -21907,27 +21946,27 @@
         <v>439</v>
       </c>
     </row>
-    <row r="58" spans="2:3">
+    <row r="58" ht="17" spans="2:3">
       <c r="B58" s="3" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="59" spans="2:3">
+    <row r="59" ht="17" spans="2:3">
       <c r="B59" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="60" spans="2:3">
+    <row r="60" ht="17" spans="2:3">
       <c r="B60" s="3" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="61" spans="2:3">
+    <row r="61" ht="17" spans="2:3">
       <c r="B61" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="62" spans="2:3">
+    <row r="62" ht="17" spans="2:3">
       <c r="B62" s="3" t="s">
         <v>444</v>
       </c>
@@ -21940,7 +21979,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" ht="17" spans="1:3">
       <c r="A68" s="3" t="s">
         <v>447</v>
       </c>
@@ -21948,7 +21987,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" ht="17" spans="1:3">
       <c r="B69" s="3" t="s">
         <v>449</v>
       </c>
@@ -21961,7 +22000,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" ht="17" spans="1:3">
       <c r="B77" s="3" t="s">
         <v>452</v>
       </c>
@@ -21969,72 +22008,72 @@
         <v>453</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" ht="17" spans="1:3">
       <c r="B79" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" ht="17" spans="1:1">
       <c r="A83" s="3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" ht="17" spans="1:1">
       <c r="A85" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" ht="17" spans="1:1">
       <c r="A87" s="3" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" ht="17" spans="1:1">
       <c r="A89" s="3" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" ht="17" spans="1:1">
       <c r="A91" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" ht="17" spans="1:1">
       <c r="A93" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" ht="17" spans="1:1">
       <c r="A95" s="3" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" ht="17" spans="1:1">
       <c r="A97" s="3" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" ht="17" spans="1:1">
       <c r="A99" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" ht="17" spans="1:1">
       <c r="A102" s="3" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" ht="17" spans="1:1">
       <c r="A104" s="3" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" ht="17" spans="1:1">
       <c r="A106" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" ht="17" spans="1:1">
       <c r="A108" s="3" t="s">
         <v>467</v>
       </c>
@@ -22059,12 +22098,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:3">
+    <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>468</v>
       </c>
@@ -22073,7 +22112,7 @@
       </c>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" ht="18.75" spans="1:3">
+    <row r="2" ht="17" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>470</v>
       </c>
@@ -22082,7 +22121,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" ht="18.75" spans="1:3">
+    <row r="3" ht="17" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>472</v>
       </c>
@@ -22091,7 +22130,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" ht="18.75" spans="1:3">
+    <row r="4" ht="17" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>474</v>
       </c>
@@ -22100,7 +22139,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" ht="18.75" spans="1:3">
+    <row r="5" ht="17" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>476</v>
       </c>
@@ -22119,14 +22158,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:C13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="45.75" style="3" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" ht="17" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>478</v>
       </c>
@@ -22137,7 +22176,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" ht="17" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>480</v>
       </c>
@@ -22148,7 +22187,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" ht="17" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>482</v>
       </c>
@@ -22159,7 +22198,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" ht="17" spans="1:3">
       <c r="A5" s="3" t="s">
         <v>484</v>
       </c>
@@ -22170,7 +22209,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" ht="17" spans="1:3">
       <c r="A6" s="3" t="s">
         <v>486</v>
       </c>
@@ -22181,7 +22220,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" ht="17" spans="1:3">
       <c r="A7" s="3" t="s">
         <v>488</v>
       </c>
@@ -22192,7 +22231,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" ht="17" spans="1:3">
       <c r="A8" s="3" t="s">
         <v>490</v>
       </c>
@@ -22203,7 +22242,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" ht="17" spans="1:3">
       <c r="A9" s="3" t="s">
         <v>492</v>
       </c>
@@ -22214,7 +22253,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" ht="17" spans="1:3">
       <c r="A10" s="3" t="s">
         <v>494</v>
       </c>
@@ -22225,7 +22264,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" ht="17" spans="1:3">
       <c r="A11" s="3" t="s">
         <v>496</v>
       </c>
@@ -22236,7 +22275,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" ht="17" spans="1:3">
       <c r="A12" s="5" t="s">
         <v>498</v>
       </c>
@@ -22261,7 +22300,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="50.875" customWidth="1"/>
   </cols>
